--- a/data/trans_camb/P15B_3_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P15B_3_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-12,85</t>
+          <t>-14,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,92</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,22</t>
+          <t>-7,91</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 5,91</t>
+          <t>-41,68; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -9,14</t>
+          <t>-56,78; -8,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 14,53</t>
+          <t>-39,2; 13,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,95</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,89</t>
+          <t>1,67; 15,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,14</t>
+          <t>2,17; 12,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 4,12</t>
+          <t>-28,66; 3,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,93; -2,43</t>
+          <t>-34,45; -2,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 10,38</t>
+          <t>-25,48; 11,36</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-28,78%</t>
+          <t>-31,91%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-27,42%</t>
+          <t>-30,06%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,52; 27,99</t>
+          <t>-69,98; 37,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-91,48; -27,45</t>
+          <t>-90,9; -22,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,22; 69,85</t>
+          <t>-67,18; 70,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 30,8</t>
+          <t>-70,56; 33,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,52; -8,36</t>
+          <t>-86,21; 4,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 76,87</t>
+          <t>-69,33; 88,51</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,33</t>
+          <t>-12,29</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,96</t>
+          <t>-7,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 1,81</t>
+          <t>-32,55; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 4,49</t>
+          <t>-35,57; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 5,44</t>
+          <t>-30,69; 5,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 4,69</t>
+          <t>-17,76; 5,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 0,0</t>
+          <t>-22,7; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 10,73</t>
+          <t>-13,2; 11,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,75; -0,85</t>
+          <t>-24,28; -0,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,59; -1,42</t>
+          <t>-25,59; -1,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 3,79</t>
+          <t>-21,66; 3,53</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-35,07%</t>
+          <t>-34,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,71%</t>
+          <t>-33,37%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 10,96</t>
+          <t>-70,03; 11,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 26,26</t>
+          <t>-75,86; 7,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 22,62</t>
+          <t>-68,26; 26,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 1,03</t>
+          <t>-72,66; -2,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,05; -5,32</t>
+          <t>-80,33; -4,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 29,57</t>
+          <t>-66,57; 27,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-21,35</t>
+          <t>-23,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-22,43</t>
+          <t>-22,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-23,86</t>
+          <t>-24,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 3,64</t>
+          <t>-44,58; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -3,35</t>
+          <t>-53,33; -2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 6,41</t>
+          <t>-47,19; 3,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-39,43; 1,14</t>
+          <t>-37,66; 1,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 10,46</t>
+          <t>-31,84; 9,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,94; -7,1</t>
+          <t>-45,99; -7,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,59; -3,52</t>
+          <t>-35,33; -4,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -2,73</t>
+          <t>-35,24; -2,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-40,17; -8,99</t>
+          <t>-40,15; -10,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-47,47%</t>
+          <t>-52,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-85,98%</t>
+          <t>-87,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-67,25%</t>
+          <t>-70,33%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 16,93</t>
+          <t>-72,13; 8,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,31; -0,51</t>
+          <t>-89,82; 1,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 24,88</t>
+          <t>-83,17; 17,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-92,05; 46,08</t>
+          <t>-91,83; 38,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,4; 91,7</t>
+          <t>-84,31; 92,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -40,78</t>
+          <t>-100,0; -46,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,98; -9,98</t>
+          <t>-74,96; -19,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,04; -9,56</t>
+          <t>-78,42; -3,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,29; -28,91</t>
+          <t>-88,22; -39,62</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 19,58</t>
+          <t>-6,76; 21,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 12,8</t>
+          <t>-15,31; 11,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 20,63</t>
+          <t>-8,86; 20,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 4,88</t>
+          <t>-18,85; 4,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 16,55</t>
+          <t>-7,96; 15,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 14,58</t>
+          <t>-11,21; 13,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 11,83</t>
+          <t>-5,72; 12,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 9,76</t>
+          <t>-6,85; 10,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 13,85</t>
+          <t>-3,8; 13,7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>148,52%</t>
+          <t>142,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 623,29</t>
+          <t>-36,84; 670,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 395,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 559,06</t>
+          <t>-57,24; 603,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 376,56</t>
+          <t>-43,18; 393,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 265,6</t>
+          <t>-51,39; 338,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 404,62</t>
+          <t>-36,5; 482,57</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>-9,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,5</t>
+          <t>-7,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -1,31</t>
+          <t>-20,7; -0,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,45; -7,22</t>
+          <t>-27,08; -7,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 2,29</t>
+          <t>-19,46; 1,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,39</t>
+          <t>-13,74; 1,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,11</t>
+          <t>-11,57; 3,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 3,43</t>
+          <t>-11,41; 2,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -1,8</t>
+          <t>-15,17; -1,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -4,96</t>
+          <t>-18,4; -4,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -0,9</t>
+          <t>-15,38; -1,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-27,25%</t>
+          <t>-29,84%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,0%</t>
+          <t>-29,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-33,21%</t>
+          <t>-35,28%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -3,67</t>
+          <t>-51,9; -1,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -27,67</t>
+          <t>-70,67; -28,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 8,85</t>
+          <t>-51,93; 7,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 34,13</t>
+          <t>-80,15; 37,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 82,98</t>
+          <t>-69,68; 67,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 66,45</t>
+          <t>-67,18; 63,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -9,81</t>
+          <t>-55,48; -9,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-67,15; -25,78</t>
+          <t>-67,4; -25,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -4,4</t>
+          <t>-54,36; -3,97</t>
         </is>
       </c>
     </row>
